--- a/testCases/GlobalSQA_Banking_Test_Cases.xlsx
+++ b/testCases/GlobalSQA_Banking_Test_Cases.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>Test ID</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Verify deposit with invalid amount</t>
   </si>
   <si>
-    <t>User is logged in as a customer</t>
-  </si>
-  <si>
     <t>Ensure invalid deposit amount is not accepted</t>
   </si>
   <si>
@@ -152,6 +149,9 @@
     <t>Verify withdrawal with insufficient balance</t>
   </si>
   <si>
+    <t>User is logged in as a customer</t>
+  </si>
+  <si>
     <t>Ensure withdrawal fails when balance is insufficient</t>
   </si>
   <si>
@@ -160,7 +160,7 @@
 3. Click Withdraw</t>
   </si>
   <si>
-    <t>Amount = 5000</t>
+    <t>Amount = 2000000</t>
   </si>
   <si>
     <t>Withdrawal failed message displayed. Balance remains unchanged</t>
@@ -229,7 +229,7 @@
     <t>Verify that the manager can add a new customer with valid details</t>
   </si>
   <si>
-    <t>1. Click Add Customer.
+    <t>1. Click Add Customer button.
 2. Enter First Name: John.
 3. Enter Last Name: Doe.
 4. Enter Post Code: 12345.
@@ -238,7 +238,9 @@
 7. Click Customers.</t>
   </si>
   <si>
-    <t>First Name: John; Last Name: Doe; Post Code: 12345</t>
+    <t>First Name: John
+Last Name: Doe
+Post Code: 12345</t>
   </si>
   <si>
     <t>Customer is added successfully and appears in the Customers table with the entered details.</t>
@@ -259,7 +261,7 @@
     <t>Verify that a new account can be opened for an existing customer with a selected currency</t>
   </si>
   <si>
-    <t>1. Click Open Account.
+    <t>1. Click Open Account button.
 2. Select customer Hermoine Granger.
 3. Select currency Dollar.
 4. Click Process.
@@ -267,7 +269,8 @@
 6. Click Customers.</t>
   </si>
   <si>
-    <t>Customer: Hermoine Granger; Currency: Dollar</t>
+    <t>Customer: Hermoine Granger
+Currency: Dollar</t>
   </si>
   <si>
     <t>A new account is created successfully, and the generated account number exists for the selected customer in the Customers table.</t>
@@ -288,7 +291,7 @@
     <t>Verify that customers can be searched using different search criteria</t>
   </si>
   <si>
-    <t>1. Click Customers.
+    <t>1. Click Customers button.
 2. Enter Harry and verify matching records.
 3. Enter E55555 and verify matching records.
 4. Enter 1006 and verify matching records.</t>
@@ -309,22 +312,27 @@
     <t>Delete a customer successfully</t>
   </si>
   <si>
-    <t>Verify that a customer can be deleted using their account number</t>
-  </si>
-  <si>
-    <t>1. Click Customers.
-2. Locate the customer with account number 1005.
-3. Click Delete for the customer.
-4. Verify that the customer is removed from the list.</t>
-  </si>
-  <si>
-    <t>Account Number: 1005</t>
-  </si>
-  <si>
-    <t>The customer with account number 1005 is removed from the Customers table.</t>
-  </si>
-  <si>
-    <t>The customer with account number 1005 was removed from the Customers table.</t>
+    <t>User is logged in as a Bank Manager. The target customer Jason Peter already exists in the customer list.</t>
+  </si>
+  <si>
+    <t>Verify that a manager can delete an existing customer from the customer table</t>
+  </si>
+  <si>
+    <t>1. Click the Customers button.
+2. Locate the customer Jason Peter.
+3. Click the Delete button for Jason Peter.
+4. Verify that Jason Peter is removed from the customer list.</t>
+  </si>
+  <si>
+    <t>First Name: Jason
+Last Name: Peter
+Post Code: E78H47</t>
+  </si>
+  <si>
+    <t>The selected customer is successfully removed from the Customers list.</t>
+  </si>
+  <si>
+    <t>Customer deleted successfully.</t>
   </si>
 </sst>
 </file>
@@ -1462,9 +1470,10 @@
   <cols>
     <col min="1" max="1" width="19.1296296296296" customWidth="1"/>
     <col min="2" max="2" width="24.75" customWidth="1"/>
-    <col min="3" max="3" width="22.75" customWidth="1"/>
+    <col min="3" max="3" width="30.7777777777778" customWidth="1"/>
     <col min="4" max="4" width="24.6296296296296" customWidth="1"/>
-    <col min="5" max="5" width="34.6296296296296" customWidth="1"/>
+    <col min="5" max="5" width="50.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="31.1296296296296" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
     <col min="10" max="10" width="27.3796296296296" customWidth="1"/>
@@ -1558,54 +1567,54 @@
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="52.5" customHeight="1" spans="1:26">
       <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>18</v>
@@ -1616,13 +1625,13 @@
     </row>
     <row r="5" ht="63" customHeight="1" spans="1:26">
       <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>39</v>
@@ -1814,22 +1823,22 @@
         <v>85</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
